--- a/BOM/Press_CPU_BOM_VER1.0_лист_закупки.xlsx
+++ b/BOM/Press_CPU_BOM_VER1.0_лист_закупки.xlsx
@@ -1,26 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EV-TECH\Desktop\Проекты\Press_CPU\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\i.fedichev\Desktop\Проекты\Press_CPU\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A31F2DB-8F75-4E22-AE0E-0F6000830016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94559C77-F15D-4791-AB7D-40795BF5B707}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4596" yWindow="3396" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="110">
   <si>
     <t>Reference</t>
   </si>
@@ -232,9 +240,6 @@
     <t>Inductor_SMD:L_1210_3225Metric_Pad1.42x2.65mm_HandSolder</t>
   </si>
   <si>
-    <t>R1,R2,R6</t>
-  </si>
-  <si>
     <t>1k</t>
   </si>
   <si>
@@ -244,18 +249,9 @@
     <t>R3</t>
   </si>
   <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>R32,R35,R38,R41,R43,R45,R50,R52,R53,R55,R56,R58,R59,R61,R65</t>
-  </si>
-  <si>
     <t>1.8k</t>
   </si>
   <si>
-    <t>R34,R36,R37,R39,R42,R44,R46,R51,R54,R57,R60,R62,R63,R66</t>
-  </si>
-  <si>
     <t>3.6k</t>
   </si>
   <si>
@@ -329,13 +325,46 @@
   </si>
   <si>
     <t>FYLS-0603UYC</t>
+  </si>
+  <si>
+    <t>Дата закупки</t>
+  </si>
+  <si>
+    <t>Нужно закупить</t>
+  </si>
+  <si>
+    <t>Количество образцов</t>
+  </si>
+  <si>
+    <t>Срок (дней)</t>
+  </si>
+  <si>
+    <t>8.2k</t>
+  </si>
+  <si>
+    <t>36k</t>
+  </si>
+  <si>
+    <t>R1,R2,R4,R6</t>
+  </si>
+  <si>
+    <t>R41,R43,R45</t>
+  </si>
+  <si>
+    <t>R32,R35,R38,R50,R52,R53,R55,R56,R58,R59,R61,R65</t>
+  </si>
+  <si>
+    <t>R42,R44,R46</t>
+  </si>
+  <si>
+    <t>R34,R36,R37,R39,R51,R54,R57,R60,R62,R63,R66</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -348,16 +377,36 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -380,11 +429,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -392,13 +484,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -705,7 +811,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" customWidth="1"/>
@@ -713,42 +819,54 @@
     <col min="3" max="3" width="23.77734375" customWidth="1"/>
     <col min="5" max="5" width="24.88671875" customWidth="1"/>
     <col min="6" max="6" width="24.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="15.21875" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="I1" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -758,7 +876,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>10</v>
@@ -767,14 +885,24 @@
         <v>18</v>
       </c>
       <c r="H2" s="1"/>
-      <c r="I2" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J2" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I2" s="1">
+        <f>$M$2*G2</f>
+        <v>90</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K2" s="3">
+        <v>100</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -784,7 +912,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
@@ -793,14 +921,21 @@
         <v>2</v>
       </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="4">
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I34" si="0">$M$2*G3</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J3" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="3">
+        <v>20</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -810,7 +945,7 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -819,14 +954,21 @@
         <v>4</v>
       </c>
       <c r="H4" s="1"/>
-      <c r="I4" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J4" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I4" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K4" s="3">
+        <v>30</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -836,7 +978,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
@@ -845,14 +987,21 @@
         <v>1</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="I5" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K5" s="3">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -862,7 +1011,7 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>10</v>
@@ -871,14 +1020,21 @@
         <v>2</v>
       </c>
       <c r="H6" s="1"/>
-      <c r="I6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" s="4">
+      <c r="I6" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="J6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="3">
+        <v>20</v>
+      </c>
+      <c r="L6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -888,7 +1044,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>21</v>
@@ -897,14 +1053,21 @@
         <v>4</v>
       </c>
       <c r="H7" s="1"/>
-      <c r="I7" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I7" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="3">
+        <v>30</v>
+      </c>
+      <c r="L7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -912,11 +1075,11 @@
         <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>24</v>
@@ -925,14 +1088,21 @@
         <v>1</v>
       </c>
       <c r="H8" s="1"/>
-      <c r="I8" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J8" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I8" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="3">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -942,7 +1112,7 @@
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
@@ -951,14 +1121,21 @@
         <v>7</v>
       </c>
       <c r="H9" s="1"/>
-      <c r="I9" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J9" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I9" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="3">
+        <v>40</v>
+      </c>
+      <c r="L9" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -979,14 +1156,15 @@
         <v>1</v>
       </c>
       <c r="H10" s="1"/>
-      <c r="I10" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J10" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I10" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1007,14 +1185,15 @@
         <v>1</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J11" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -1033,14 +1212,19 @@
         <v>5</v>
       </c>
       <c r="H12" s="1"/>
-      <c r="I12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J12" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I12" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="3">
+        <v>30</v>
+      </c>
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>39</v>
       </c>
@@ -1048,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
@@ -1061,14 +1245,19 @@
         <v>1</v>
       </c>
       <c r="H13" s="1"/>
-      <c r="I13" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I13" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="3">
+        <v>10</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>42</v>
       </c>
@@ -1087,14 +1276,17 @@
         <v>1</v>
       </c>
       <c r="H14" s="1"/>
-      <c r="I14" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I14" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="9"/>
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>45</v>
       </c>
@@ -1113,14 +1305,19 @@
         <v>1</v>
       </c>
       <c r="H15" s="1"/>
-      <c r="I15" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J15" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I15" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" s="3">
+        <v>10</v>
+      </c>
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -1128,7 +1325,7 @@
         <v>28</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
@@ -1141,14 +1338,19 @@
         <v>1</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I16" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" s="3">
+        <v>10</v>
+      </c>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>50</v>
       </c>
@@ -1169,14 +1371,19 @@
         <v>2</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J17" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I17" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="3">
+        <v>15</v>
+      </c>
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>54</v>
       </c>
@@ -1195,14 +1402,19 @@
         <v>2</v>
       </c>
       <c r="H18" s="1"/>
-      <c r="I18" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J18" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I18" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" s="3">
+        <v>15</v>
+      </c>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>57</v>
       </c>
@@ -1221,14 +1433,21 @@
         <v>1</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J19" s="4">
+      <c r="I19" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" s="3">
+        <v>5</v>
+      </c>
+      <c r="L19" s="3">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>60</v>
       </c>
@@ -1247,14 +1466,19 @@
         <v>2</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J20" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I20" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K20" s="3">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>63</v>
       </c>
@@ -1273,14 +1497,19 @@
         <v>1</v>
       </c>
       <c r="H21" s="1"/>
-      <c r="I21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J21" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I21" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="3">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>67</v>
       </c>
@@ -1299,42 +1528,54 @@
         <v>1</v>
       </c>
       <c r="H22" s="1"/>
-      <c r="I22" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J22" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="I22" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="3">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="3">
+        <v>30</v>
+      </c>
+      <c r="L23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="G23" s="1">
-        <v>3</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J23" s="4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="B24" s="1">
         <v>120</v>
@@ -1342,254 +1583,352 @@
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
       </c>
       <c r="H24" s="1"/>
-      <c r="I24" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J24" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="1">
-        <v>750</v>
+      <c r="I24" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="3">
+        <v>10</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G25" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="1"/>
-      <c r="I25" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>76</v>
+      <c r="I25" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="3">
+        <v>20</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G26" s="1">
+        <v>3</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="H26" s="1"/>
-      <c r="I26" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>78</v>
+      <c r="J26" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="3">
+        <v>20</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>80</v>
+      <c r="I27" s="1">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G28" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H28" s="1"/>
-      <c r="I28" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J28" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I28" s="1">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K28" s="3">
+        <v>100</v>
+      </c>
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>82</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="C29" s="1"/>
       <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="F29" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G29" s="1">
         <v>1</v>
       </c>
       <c r="H29" s="1"/>
-      <c r="I29" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J29" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I29" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K29" s="3">
+        <v>10</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="G30" s="1">
         <v>1</v>
       </c>
       <c r="H30" s="1"/>
-      <c r="I30" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J30" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I30" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" s="3">
+        <v>6</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>87</v>
+      <c r="C31" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K31" s="3">
         <v>6</v>
       </c>
-      <c r="H31" s="1"/>
-      <c r="I31" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J31" s="4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G32" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" s="1"/>
-      <c r="I32" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="J32" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I32" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K32" s="3">
+        <v>40</v>
+      </c>
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>92</v>
+      <c r="C33" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1" t="s">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="G33" s="1">
         <v>1</v>
       </c>
       <c r="H33" s="1"/>
-      <c r="I33" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="J33" s="4">
-        <v>5</v>
+      <c r="I33" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K34" s="3">
+        <v>6</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" s="7">
+        <v>45946</v>
       </c>
     </row>
   </sheetData>
